--- a/reports/Debug-snowbowl-20260106/Month to Date (Prior Year)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20260106/Month to Date (Prior Year)_Visits.xlsx
@@ -37,10 +37,10 @@
     <t>Snowbowl Comp Tickets</t>
   </si>
   <si>
-    <t>Snowbowl Tickets</t>
+    <t>Snowbowl Uplift Tickets</t>
   </si>
   <si>
-    <t>Snowbowl Uplift Tickets</t>
+    <t>Snowbowl Tickets</t>
   </si>
 </sst>
 </file>
@@ -473,13 +473,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>45660</v>
+        <v>45659</v>
       </c>
       <c r="C5" s="2">
-        <v>529</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -487,10 +487,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>45663</v>
+        <v>45660</v>
       </c>
       <c r="C6" s="2">
-        <v>6</v>
+        <v>1426</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -501,13 +501,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>45663</v>
+        <v>45662</v>
       </c>
       <c r="C7" s="2">
-        <v>287</v>
+        <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,7 +518,7 @@
         <v>45658</v>
       </c>
       <c r="C8" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -529,10 +529,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C9" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>5</v>
@@ -543,13 +543,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C10" s="2">
-        <v>1426</v>
+        <v>322</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -557,10 +557,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>45662</v>
+        <v>45660</v>
       </c>
       <c r="C11" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
@@ -571,10 +571,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C12" s="2">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -585,10 +585,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>45658</v>
+        <v>45661</v>
       </c>
       <c r="C13" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>5</v>
@@ -599,13 +599,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>45658</v>
+        <v>45663</v>
       </c>
       <c r="C14" s="2">
-        <v>322</v>
+        <v>47</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -613,10 +613,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C15" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -627,10 +627,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C16" s="2">
-        <v>79</v>
+        <v>1102</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>5</v>
@@ -641,13 +641,13 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C17" s="2">
+        <v>236</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -655,10 +655,10 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>45663</v>
+        <v>45661</v>
       </c>
       <c r="C18" s="2">
-        <v>47</v>
+        <v>902</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>5</v>
@@ -669,13 +669,13 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>45658</v>
+        <v>45661</v>
       </c>
       <c r="C19" s="2">
-        <v>7</v>
+        <v>1268</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -686,7 +686,7 @@
         <v>45658</v>
       </c>
       <c r="C20" s="2">
-        <v>1304</v>
+        <v>247</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>7</v>
@@ -700,7 +700,7 @@
         <v>45659</v>
       </c>
       <c r="C21" s="2">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>5</v>
@@ -714,7 +714,7 @@
         <v>45659</v>
       </c>
       <c r="C22" s="2">
-        <v>7</v>
+        <v>1069</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>5</v>
@@ -725,13 +725,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="C23" s="2">
-        <v>509</v>
+        <v>7</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -739,13 +739,13 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C24" s="2">
-        <v>5</v>
+        <v>1377</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -753,10 +753,10 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>45662</v>
+        <v>45661</v>
       </c>
       <c r="C25" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>5</v>
@@ -767,13 +767,13 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>45662</v>
+        <v>45661</v>
       </c>
       <c r="C26" s="2">
-        <v>5</v>
+        <v>248</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,10 +784,10 @@
         <v>45662</v>
       </c>
       <c r="C27" s="2">
-        <v>239</v>
+        <v>60</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -795,13 +795,13 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>45663</v>
+        <v>45662</v>
       </c>
       <c r="C28" s="2">
-        <v>63</v>
+        <v>866</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -809,10 +809,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>45658</v>
+        <v>45663</v>
       </c>
       <c r="C29" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -823,13 +823,13 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>45658</v>
+        <v>45663</v>
       </c>
       <c r="C30" s="2">
-        <v>1102</v>
+        <v>1828</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -837,13 +837,13 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C31" s="2">
-        <v>236</v>
+        <v>7</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -851,13 +851,13 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>45661</v>
+        <v>45658</v>
       </c>
       <c r="C32" s="2">
-        <v>902</v>
+        <v>1304</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -865,13 +865,13 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>45661</v>
+        <v>45659</v>
       </c>
       <c r="C33" s="2">
-        <v>1268</v>
+        <v>7</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -879,13 +879,13 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="C34" s="2">
-        <v>247</v>
+        <v>7</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -896,10 +896,10 @@
         <v>45659</v>
       </c>
       <c r="C35" s="2">
-        <v>52</v>
+        <v>509</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -907,10 +907,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>45659</v>
+        <v>45661</v>
       </c>
       <c r="C36" s="2">
-        <v>1069</v>
+        <v>5</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>5</v>
@@ -921,10 +921,10 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>45660</v>
+        <v>45662</v>
       </c>
       <c r="C37" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -935,13 +935,13 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>45660</v>
+        <v>45662</v>
       </c>
       <c r="C38" s="2">
-        <v>1377</v>
+        <v>5</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -949,13 +949,13 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>45661</v>
+        <v>45662</v>
       </c>
       <c r="C39" s="2">
+        <v>239</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -963,13 +963,13 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>45661</v>
+        <v>45663</v>
       </c>
       <c r="C40" s="2">
-        <v>248</v>
+        <v>63</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -977,10 +977,10 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>45662</v>
+        <v>45658</v>
       </c>
       <c r="C41" s="2">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>5</v>
@@ -991,13 +991,13 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>45662</v>
+        <v>45660</v>
       </c>
       <c r="C42" s="2">
-        <v>866</v>
+        <v>529</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1022,10 +1022,10 @@
         <v>45663</v>
       </c>
       <c r="C44" s="2">
-        <v>1828</v>
+        <v>287</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1067,7 +1067,7 @@
         <v>1510</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1081,7 +1081,7 @@
         <v>196</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1137,7 +1137,7 @@
         <v>862</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1151,7 +1151,7 @@
         <v>57</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:4">
